--- a/Results/Figures.out/dat.out.xlsx
+++ b/Results/Figures.out/dat.out.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">species</t>
   </si>
@@ -35,46 +35,115 @@
     <t xml:space="preserve">all.coef.cp.kg</t>
   </si>
   <si>
+    <t xml:space="preserve">mean.coef.bw.kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.adg.g.d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.ndf.g.kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.cp.g.kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.bw.kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.adg.g.d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.ndf.g.kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.cp.g.kg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sheep</t>
   </si>
   <si>
     <t xml:space="preserve">low</t>
   </si>
   <si>
-    <t xml:space="preserve">14.68 ± 9.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26 ± 0.18***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.16 ± 0.07***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.75 ± 0.14***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12 ± 0.31***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.17 ± 0.07***</t>
+    <t xml:space="preserve">13.92 ± 13.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17 ± 0.5***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.22 ± 0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.36 ± 2.18***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67 ± 0.24***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.48 ± 0.08***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.95 ± 0.06***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81 ± 0.1***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.54 ± 0.51***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72 ± 0.91***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.52 ± 0.06***</t>
   </si>
   <si>
     <t xml:space="preserve">hi</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41 ± 0.3***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.34 ± 0.06***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36 ± 0.01***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51 ± 0.05***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.16 ± 0.02***</t>
+    <t xml:space="preserve">8.16 ± 0.92***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 ± 0.04***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.28 ± 0.14***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13 ± 7.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79 ± 0.5***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.32 ± 0.15***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.65 ± 0.06***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48 ± 2.87***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47 ± 0.04***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4 ± 0.07***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.64 ± 0.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.3 ± 6.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6 ± 0.19***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06 ± 0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.25 ± 0.47</t>
   </si>
 </sst>
 </file>
@@ -425,88 +494,382 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G2"/>
+      <c r="H2" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="K2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="L2" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3"/>
+        <v>21</v>
+      </c>
+      <c r="F3"/>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N3"/>
+      <c r="O3" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4"/>
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
       <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4"/>
+        <v>24</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N4"/>
+      <c r="O4" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5"/>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5"/>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="L5"/>
+      <c r="M5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="n">
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="K6" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5"/>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results/Figures.out/dat.out.xlsx
+++ b/Results/Figures.out/dat.out.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">species</t>
   </si>
@@ -65,85 +65,79 @@
     <t xml:space="preserve">low</t>
   </si>
   <si>
-    <t xml:space="preserve">13.92 ± 13.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17 ± 0.5***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.22 ± 0.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.36 ± 2.18***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67 ± 0.24***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.48 ± 0.08***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.95 ± 0.06***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81 ± 0.1***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.54 ± 0.51***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72 ± 0.91***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.52 ± 0.06***</t>
+    <t xml:space="preserve">12.24 ± 10.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32 ± 0.02***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.27 ± 0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.34 ± 2.42***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77 ± 0.22***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.53 ± 0.47***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.88 ± 1.8***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74 ± 0.17***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.54 ± 0.3***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87 ± 0.21***</t>
   </si>
   <si>
     <t xml:space="preserve">hi</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16 ± 0.92***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5 ± 0.04***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.28 ± 0.14***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13 ± 7.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79 ± 0.5***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.32 ± 0.15***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.65 ± 0.06***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48 ± 2.87***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47 ± 0.04***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.4 ± 0.07***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.64 ± 0.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.3 ± 6.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6 ± 0.19***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06 ± 0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.25 ± 0.47</t>
+    <t xml:space="preserve">10.51 ± 9.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48 ± 0.02***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.33 ± 0.19***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11 ± 1.92***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48 ± 0.11***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.41 ± 0.23***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.83 ± 0.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77 ± 3.59***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62 ± 0.39***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.37 ± 0.16***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.78 ± 0.41***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94 ± 0.25***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 ± 0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.32 ± 0.61</t>
   </si>
 </sst>
 </file>
@@ -540,25 +534,25 @@
       </c>
       <c r="G2"/>
       <c r="H2" t="n">
-        <v>13.92</v>
+        <v>12.24</v>
       </c>
       <c r="I2" t="n">
-        <v>3.17</v>
+        <v>3.32</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="K2" t="e">
         <v>#NUM!</v>
       </c>
       <c r="L2" t="n">
-        <v>13.47</v>
+        <v>10.53</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="N2" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="O2"/>
     </row>
@@ -583,26 +577,26 @@
         <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>15.36</v>
+        <v>14.34</v>
       </c>
       <c r="I3" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="J3" t="e">
         <v>#NUM!</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.48</v>
+        <v>-1.53</v>
       </c>
       <c r="L3" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="N3"/>
       <c r="O3" t="n">
-        <v>0.08</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="4">
@@ -626,10 +620,10 @@
         <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>13.95</v>
+        <v>14.88</v>
       </c>
       <c r="I4" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="J4" t="e">
         <v>#NUM!</v>
@@ -638,14 +632,14 @@
         <v>-1.54</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -663,70 +657,66 @@
         <v>26</v>
       </c>
       <c r="F5"/>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
+      <c r="G5"/>
       <c r="H5" t="e">
         <v>#NUM!</v>
       </c>
       <c r="I5" t="n">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="J5" t="e">
         <v>#NUM!</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.52</v>
+        <v>-0.8</v>
       </c>
       <c r="L5"/>
       <c r="M5" t="n">
-        <v>0.91</v>
+        <v>0.21</v>
       </c>
       <c r="N5"/>
-      <c r="O5" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="O5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
       </c>
       <c r="G6"/>
       <c r="H6" t="n">
-        <v>8.16</v>
+        <v>10.51</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.28</v>
+        <v>-0.33</v>
       </c>
       <c r="K6" t="e">
         <v>#NUM!</v>
       </c>
       <c r="L6" t="n">
-        <v>0.92</v>
+        <v>9.82</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="N6" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="O6"/>
     </row>
@@ -735,46 +725,46 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>33</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>34</v>
       </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
       <c r="H7" t="n">
-        <v>7.13</v>
+        <v>9.11</v>
       </c>
       <c r="I7" t="n">
-        <v>2.79</v>
+        <v>2.48</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.32</v>
+        <v>-0.41</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.65</v>
+        <v>-0.83</v>
       </c>
       <c r="L7" t="n">
-        <v>7.58</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c r="N7" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="8">
@@ -782,46 +772,46 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>37</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>38</v>
       </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
       <c r="H8" t="n">
-        <v>9.48</v>
+        <v>9.77</v>
       </c>
       <c r="I8" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.64</v>
+        <v>-0.78</v>
       </c>
       <c r="L8" t="n">
-        <v>2.87</v>
+        <v>3.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04</v>
+        <v>0.39</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07</v>
+        <v>0.16</v>
       </c>
       <c r="O8" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="9">
@@ -829,46 +819,42 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9"/>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
       <c r="H9" t="n">
-        <v>-4.3</v>
+        <v>0.66</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>0.94</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.68</v>
-      </c>
+        <v>-0.32</v>
+      </c>
+      <c r="L9"/>
       <c r="M9" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Figures.out/dat.out.xlsx
+++ b/Results/Figures.out/dat.out.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">species</t>
   </si>
@@ -65,79 +65,73 @@
     <t xml:space="preserve">low</t>
   </si>
   <si>
-    <t xml:space="preserve">12.24 ± 10.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32 ± 0.02***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27 ± 0.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.34 ± 2.42***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77 ± 0.22***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.53 ± 0.47***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.88 ± 1.8***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74 ± 0.17***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.54 ± 0.3***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87 ± 0.21***</t>
+    <t xml:space="preserve">19.94 ± 7.38***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12 ± 0.29***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.17 ± 0.03***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.42 ± 8.04***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02 ± 0.27***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.18 ± 2.26***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93 ± 0.22***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 ± 0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 ± 0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.58 ± 2.64***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 ± 0</t>
   </si>
   <si>
     <t xml:space="preserve">hi</t>
   </si>
   <si>
-    <t xml:space="preserve">10.51 ± 9.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48 ± 0.02***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.33 ± 0.19***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11 ± 1.92***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48 ± 0.11***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.41 ± 0.23***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.83 ± 0.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77 ± 3.59***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62 ± 0.39***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.37 ± 0.16***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.78 ± 0.41***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94 ± 0.25***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02 ± 0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.32 ± 0.61</t>
+    <t xml:space="preserve">16.81 ± 1.45***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75 ± 0.11***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14 ± 0.07***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.93 ± 4.03***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7 ± 0.17***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.22 ± 0.08***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.72 ± 2.71***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76 ± 0.09***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14 ± 0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.19 ± 0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5 ± 1.48***</t>
   </si>
 </sst>
 </file>
@@ -534,25 +528,25 @@
       </c>
       <c r="G2"/>
       <c r="H2" t="n">
-        <v>12.24</v>
+        <v>19.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.27</v>
+        <v>-0.17</v>
       </c>
       <c r="K2" t="e">
         <v>#NUM!</v>
       </c>
       <c r="L2" t="n">
-        <v>10.53</v>
+        <v>7.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="N2" t="n">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="O2"/>
     </row>
@@ -573,31 +567,27 @@
         <v>21</v>
       </c>
       <c r="F3"/>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
+      <c r="G3"/>
       <c r="H3" t="n">
-        <v>14.34</v>
+        <v>19.42</v>
       </c>
       <c r="I3" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="J3" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="K3" t="n">
-        <v>-1.53</v>
+      <c r="K3" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="L3" t="n">
-        <v>2.42</v>
+        <v>8.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="N3"/>
-      <c r="O3" t="n">
-        <v>0.47</v>
-      </c>
+      <c r="O3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -610,36 +600,40 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="F4"/>
       <c r="G4" t="s">
         <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>14.88</v>
+        <v>21.18</v>
       </c>
       <c r="I4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J4" t="e">
-        <v>#NUM!</v>
+        <v>2.93</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.54</v>
+        <v>-0.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="N4"/>
+        <v>0.22</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.13</v>
+      </c>
       <c r="O4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5">
@@ -652,29 +646,37 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5"/>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
       <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5"/>
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
       <c r="G5"/>
-      <c r="H5" t="e">
+      <c r="H5" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="I5" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="J5" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="L5"/>
+      <c r="L5" t="n">
+        <v>2.64</v>
+      </c>
       <c r="M5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="N5"/>
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
       <c r="O5"/>
     </row>
     <row r="6">
@@ -682,41 +684,41 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6"/>
       <c r="H6" t="n">
-        <v>10.51</v>
+        <v>16.81</v>
       </c>
       <c r="I6" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.33</v>
+        <v>0.14</v>
       </c>
       <c r="K6" t="e">
         <v>#NUM!</v>
       </c>
       <c r="L6" t="n">
-        <v>9.82</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="N6" t="n">
-        <v>0.19</v>
+        <v>0.07</v>
       </c>
       <c r="O6"/>
     </row>
@@ -725,46 +727,42 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
         <v>33</v>
       </c>
+      <c r="F7"/>
       <c r="G7" t="s">
         <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>9.11</v>
+        <v>14.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.41</v>
+        <v>2.7</v>
+      </c>
+      <c r="J7" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.83</v>
+        <v>-0.22</v>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>4.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.23</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="N7"/>
       <c r="O7" t="n">
-        <v>0.77</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +770,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -790,28 +788,28 @@
         <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>9.77</v>
+        <v>16.72</v>
       </c>
       <c r="I8" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.37</v>
+        <v>0.14</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.78</v>
+        <v>-0.19</v>
       </c>
       <c r="L8" t="n">
-        <v>3.59</v>
+        <v>2.71</v>
       </c>
       <c r="M8" t="n">
-        <v>0.39</v>
+        <v>0.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="O8" t="n">
-        <v>0.41</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -819,43 +817,43 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
-      <c r="D9"/>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G9"/>
       <c r="H9" t="n">
-        <v>0.66</v>
+        <v>21.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="L9"/>
+        <v>0</v>
+      </c>
+      <c r="K9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.48</v>
+      </c>
       <c r="M9" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.61</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
